--- a/data/saeop/노인일자리.xlsx
+++ b/data/saeop/노인일자리.xlsx
@@ -880,7 +880,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>노인일자리팀 033-747-0516</t>
+          <t>노인일자리팀 033-747-3636</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>033-747-0516</t>
+          <t>033-747-3636</t>
         </is>
       </c>
       <c r="J6" s="8" t="n"/>

--- a/data/saeop/노인일자리.xlsx
+++ b/data/saeop/노인일자리.xlsx
@@ -801,7 +801,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>KakaoTalk_20261013_131524680.jpg</v>
+        <v>KakaoTalk_20261013_132702304_03.jpg</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -833,7 +833,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>KakaoTalk_20261013_131511292.jpg</v>
+        <v>KakaoTalk_20261013_132702304_01.jpg</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -865,7 +865,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>KakaoTalk_20260506_114714426.jpg</v>
+        <v>KakaoTalk_20261013_131511292.jpg</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -897,7 +897,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>KakaoTalk_20261013_131002860.jpg</v>
+        <v>KakaoTalk_20260506_114714426.jpg</v>
       </c>
       <c r="H13" t="str">
         <v/>
